--- a/exports/trend_1d/ICICILIFE_full_report.xlsx
+++ b/exports/trend_1d/ICICILIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.14</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42690</v>
+        <v>42691</v>
       </c>
       <c r="H2" t="n">
-        <v>299.3</v>
+        <v>293.5</v>
       </c>
       <c r="I2" t="n">
         <v>297.0526811295</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.640000000000001</v>
+        <v>-10.41</v>
       </c>
       <c r="L2" t="n">
         <v>17.28</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.71</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42720</v>
+        <v>42723</v>
       </c>
       <c r="H3" t="n">
-        <v>310.55</v>
+        <v>315.5</v>
       </c>
       <c r="I3" t="n">
         <v>314.2367351079528</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.81</v>
+        <v>-7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>7.31</v>
+        <v>8.33</v>
       </c>
       <c r="M3" t="n">
         <v>0.89</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42941</v>
+        <v>42942</v>
       </c>
       <c r="H4" t="n">
-        <v>468.1</v>
+        <v>450.35</v>
       </c>
       <c r="I4" t="n">
         <v>451.0959782743568</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K4" t="n">
-        <v>48.37</v>
+        <v>42.74</v>
       </c>
       <c r="L4" t="n">
         <v>6.78</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.01</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43105</v>
+        <v>43108</v>
       </c>
       <c r="H5" t="n">
-        <v>394.15</v>
+        <v>411.8</v>
       </c>
       <c r="I5" t="n">
         <v>397.1068611642163</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K5" t="n">
-        <v>12.48</v>
+        <v>8.56</v>
       </c>
       <c r="L5" t="n">
         <v>5.43</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43160</v>
+        <v>43164</v>
       </c>
       <c r="H6" t="n">
-        <v>408.1</v>
+        <v>397.8</v>
       </c>
       <c r="I6" t="n">
         <v>399.5888264409727</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9</v>
+        <v>-3.4</v>
       </c>
       <c r="L6" t="n">
         <v>4.97</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.51</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43195</v>
+        <v>43196</v>
       </c>
       <c r="H7" t="n">
-        <v>393.75</v>
+        <v>400.9</v>
       </c>
       <c r="I7" t="n">
         <v>399.0053889391942</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" t="n">
-        <v>1.02</v>
+        <v>-0.78</v>
       </c>
       <c r="L7" t="n">
         <v>2.75</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.58</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43242</v>
+        <v>43243</v>
       </c>
       <c r="H8" t="n">
-        <v>418.85</v>
+        <v>408.35</v>
       </c>
       <c r="I8" t="n">
         <v>411.8742219463398</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K8" t="n">
-        <v>4.48</v>
+        <v>1.86</v>
       </c>
       <c r="L8" t="n">
         <v>7.21</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.84</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H9" t="n">
-        <v>374.8</v>
+        <v>385.75</v>
       </c>
       <c r="I9" t="n">
         <v>380.8868194863391</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" t="n">
-        <v>8.220000000000001</v>
+        <v>5.53</v>
       </c>
       <c r="L9" t="n">
         <v>5.24</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.05</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H10" t="n">
-        <v>384.9</v>
+        <v>378.95</v>
       </c>
       <c r="I10" t="n">
         <v>384.2871177393978</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.22</v>
+        <v>-1.76</v>
       </c>
       <c r="L10" t="n">
         <v>3.82</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.04</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H11" t="n">
-        <v>352.4</v>
+        <v>358.85</v>
       </c>
       <c r="I11" t="n">
         <v>356.0892446151967</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K11" t="n">
-        <v>7.01</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>3.1</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>12.26</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43423</v>
+        <v>43424</v>
       </c>
       <c r="H12" t="n">
-        <v>323.25</v>
+        <v>321</v>
       </c>
       <c r="I12" t="n">
         <v>322.5646879663046</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.92</v>
+        <v>-10.55</v>
       </c>
       <c r="L12" t="n">
-        <v>10.55</v>
+        <v>11.08</v>
       </c>
       <c r="M12" t="n">
         <v>0.83</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>12.85</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43473</v>
+        <v>43474</v>
       </c>
       <c r="H13" t="n">
-        <v>324.45</v>
+        <v>336.75</v>
       </c>
       <c r="I13" t="n">
         <v>335.2167648876369</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.07</v>
+        <v>-4.91</v>
       </c>
       <c r="L13" t="n">
-        <v>3.54</v>
+        <v>5.89</v>
       </c>
       <c r="M13" t="n">
         <v>1.42</v>
       </c>
       <c r="N13" t="n">
-        <v>3.39</v>
+        <v>3.79</v>
       </c>
       <c r="O13" t="n">
         <v>-0.7</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>9.35</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43487</v>
+        <v>43488</v>
       </c>
       <c r="H14" t="n">
-        <v>345</v>
+        <v>305.4</v>
       </c>
       <c r="I14" t="n">
         <v>321.7132253438226</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>2.45</v>
+        <v>-9.31</v>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>10.56</v>
       </c>
       <c r="M14" t="n">
-        <v>0.91</v>
+        <v>4.35</v>
       </c>
       <c r="N14" t="n">
-        <v>1.89</v>
+        <v>11.48</v>
       </c>
       <c r="O14" t="n">
         <v>3.79</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>17.78</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43518</v>
+        <v>43521</v>
       </c>
       <c r="H15" t="n">
-        <v>314.9</v>
+        <v>317.15</v>
       </c>
       <c r="I15" t="n">
         <v>315.4558060010371</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.11</v>
+        <v>-3.85</v>
       </c>
       <c r="L15" t="n">
         <v>10.35</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.19</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H16" t="n">
-        <v>352.1</v>
+        <v>337.2</v>
       </c>
       <c r="I16" t="n">
         <v>343.2599245250163</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
-        <v>11.02</v>
+        <v>6.32</v>
       </c>
       <c r="L16" t="n">
         <v>3.91</v>
@@ -1353,7 +1544,7 @@
         <v>3.34</v>
       </c>
       <c r="N16" t="n">
-        <v>3.98</v>
+        <v>4.23</v>
       </c>
       <c r="O16" t="n">
         <v>0.71</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>12.35</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H17" t="n">
-        <v>356.4</v>
+        <v>369.8</v>
       </c>
       <c r="I17" t="n">
         <v>366.0670848529508</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.69</v>
+        <v>-9.67</v>
       </c>
       <c r="L17" t="n">
-        <v>7.65</v>
+        <v>15.64</v>
       </c>
       <c r="M17" t="n">
         <v>1.69</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.56</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H18" t="n">
-        <v>494.9</v>
+        <v>492.45</v>
       </c>
       <c r="I18" t="n">
         <v>493.6820270819148</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K18" t="n">
-        <v>33.83</v>
+        <v>33.17</v>
       </c>
       <c r="L18" t="n">
         <v>5.21</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.23</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43851</v>
+        <v>43852</v>
       </c>
       <c r="H19" t="n">
-        <v>489.05</v>
+        <v>506.5</v>
       </c>
       <c r="I19" t="n">
         <v>502.3562982049448</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.85</v>
       </c>
       <c r="L19" t="n">
-        <v>2.93</v>
+        <v>3.97</v>
       </c>
       <c r="M19" t="n">
         <v>1.13</v>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>3.57</v>
       </c>
       <c r="O19" t="n">
         <v>-0.5</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H20" t="n">
-        <v>510.95</v>
+        <v>451.35</v>
       </c>
       <c r="I20" t="n">
         <v>492.6228546046424</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>0.88</v>
+        <v>-10.89</v>
       </c>
       <c r="L20" t="n">
-        <v>3.56</v>
+        <v>12.34</v>
       </c>
       <c r="M20" t="n">
         <v>0.42</v>
       </c>
       <c r="N20" t="n">
-        <v>2.06</v>
+        <v>11.66</v>
       </c>
       <c r="O20" t="n">
         <v>3.57</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>18.76</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H21" t="n">
-        <v>338.9</v>
+        <v>357.25</v>
       </c>
       <c r="I21" t="n">
         <v>356.3287359164424</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K21" t="n">
-        <v>24.91</v>
+        <v>20.85</v>
       </c>
       <c r="L21" t="n">
         <v>14.08</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>33.7</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H22" t="n">
-        <v>451.3</v>
+        <v>422.65</v>
       </c>
       <c r="I22" t="n">
         <v>438.966185695271</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K22" t="n">
-        <v>26.33</v>
+        <v>18.31</v>
       </c>
       <c r="L22" t="n">
         <v>11.27</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>13.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H23" t="n">
-        <v>433.55</v>
+        <v>448.95</v>
       </c>
       <c r="I23" t="n">
         <v>439.7267273777817</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.58</v>
+        <v>-6.22</v>
       </c>
       <c r="L23" t="n">
         <v>7.63</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H24" t="n">
-        <v>490.9</v>
+        <v>481</v>
       </c>
       <c r="I24" t="n">
         <v>487.4258440952566</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K24" t="n">
-        <v>9.34</v>
+        <v>7.14</v>
       </c>
       <c r="L24" t="n">
         <v>3.3</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>11.24</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
       <c r="H25" t="n">
-        <v>452.05</v>
+        <v>477.95</v>
       </c>
       <c r="I25" t="n">
         <v>474.3429760685054</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K25" t="n">
-        <v>6.02</v>
+        <v>0.63</v>
       </c>
       <c r="L25" t="n">
-        <v>6.12</v>
+        <v>7.05</v>
       </c>
       <c r="M25" t="n">
-        <v>1.34</v>
+        <v>2.98</v>
       </c>
       <c r="N25" t="n">
-        <v>3.43</v>
+        <v>5.73</v>
       </c>
       <c r="O25" t="n">
         <v>-2.02</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.27</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44482</v>
+        <v>44483</v>
       </c>
       <c r="H26" t="n">
-        <v>656.8</v>
+        <v>651.95</v>
       </c>
       <c r="I26" t="n">
         <v>652.8095314663561</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K26" t="n">
-        <v>37.42</v>
+        <v>36.41</v>
       </c>
       <c r="L26" t="n">
         <v>2.6</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H27" t="n">
-        <v>591.1</v>
+        <v>615.65</v>
       </c>
       <c r="I27" t="n">
         <v>593.8261760109963</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K27" t="n">
-        <v>9.33</v>
+        <v>5.57</v>
       </c>
       <c r="L27" t="n">
         <v>4.68</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H28" t="n">
-        <v>577.55</v>
+        <v>568.05</v>
       </c>
       <c r="I28" t="n">
         <v>571.5910455353867</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.19</v>
+        <v>-7.73</v>
       </c>
       <c r="L28" t="n">
-        <v>8.23</v>
+        <v>9.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.15</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.29</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H29" t="n">
-        <v>500.9</v>
+        <v>508</v>
       </c>
       <c r="I29" t="n">
         <v>505.1941507610306</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K29" t="n">
-        <v>11.82</v>
+        <v>10.57</v>
       </c>
       <c r="L29" t="n">
         <v>1.84</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.07</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44690</v>
+        <v>44691</v>
       </c>
       <c r="H30" t="n">
-        <v>504.85</v>
+        <v>499</v>
       </c>
       <c r="I30" t="n">
         <v>500.8335855137776</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.62</v>
+        <v>-1.77</v>
       </c>
       <c r="L30" t="n">
         <v>2.83</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>11.1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44712</v>
+        <v>44713</v>
       </c>
       <c r="H31" t="n">
-        <v>521.6</v>
+        <v>547.9</v>
       </c>
       <c r="I31" t="n">
         <v>546.4870917679664</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.53</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>7.21</v>
+        <v>10.61</v>
       </c>
       <c r="M31" t="n">
         <v>2.15</v>
       </c>
       <c r="N31" t="n">
-        <v>3.09</v>
+        <v>5.04</v>
       </c>
       <c r="O31" t="n">
         <v>-1.16</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>11.55</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44728</v>
+        <v>44729</v>
       </c>
       <c r="H32" t="n">
-        <v>519.8</v>
+        <v>507.3</v>
       </c>
       <c r="I32" t="n">
         <v>508.4853788075488</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.13</v>
+        <v>-7.41</v>
       </c>
       <c r="L32" t="n">
-        <v>7.01</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>2.69</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.92</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H33" t="n">
-        <v>530</v>
+        <v>553.6</v>
       </c>
       <c r="I33" t="n">
         <v>532.4198948504147</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.47</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>5.83</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M33" t="n">
         <v>2.06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.47</v>
+        <v>4.45</v>
       </c>
       <c r="O33" t="n">
         <v>-2.4</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H34" t="n">
-        <v>553.05</v>
+        <v>545.55</v>
       </c>
       <c r="I34" t="n">
         <v>547.617796224351</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.1</v>
+        <v>-1.45</v>
       </c>
       <c r="L34" t="n">
         <v>3.83</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.65</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44939</v>
+        <v>44942</v>
       </c>
       <c r="H35" t="n">
-        <v>469.55</v>
+        <v>477.55</v>
       </c>
       <c r="I35" t="n">
         <v>473.1258979405411</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K35" t="n">
-        <v>13.93</v>
+        <v>12.46</v>
       </c>
       <c r="L35" t="n">
         <v>1.91</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.61</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44956</v>
+        <v>44957</v>
       </c>
       <c r="H36" t="n">
-        <v>454.5</v>
+        <v>452.4</v>
       </c>
       <c r="I36" t="n">
         <v>453.9202098955388</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.83</v>
+        <v>-5.27</v>
       </c>
       <c r="L36" t="n">
         <v>6.45</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.17</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45006</v>
+        <v>45007</v>
       </c>
       <c r="H37" t="n">
-        <v>415.9</v>
+        <v>427.7</v>
       </c>
       <c r="I37" t="n">
         <v>418.2329322632689</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
-        <v>8.07</v>
+        <v>5.46</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.57</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45125</v>
+        <v>45126</v>
       </c>
       <c r="H38" t="n">
-        <v>574.75</v>
+        <v>559.45</v>
       </c>
       <c r="I38" t="n">
         <v>559.6198528938584</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K38" t="n">
-        <v>34.38</v>
+        <v>30.8</v>
       </c>
       <c r="L38" t="n">
         <v>8.58</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.38</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H39" t="n">
-        <v>556.7</v>
+        <v>576.55</v>
       </c>
       <c r="I39" t="n">
         <v>575.2290225140011</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K39" t="n">
-        <v>0.49</v>
+        <v>-3.06</v>
       </c>
       <c r="L39" t="n">
         <v>4.78</v>
       </c>
       <c r="M39" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="N39" t="n">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="O39" t="n">
         <v>-2.66</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45205</v>
+        <v>45208</v>
       </c>
       <c r="H40" t="n">
-        <v>559.35</v>
+        <v>543.8</v>
       </c>
       <c r="I40" t="n">
         <v>546.1917599539657</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.98</v>
+        <v>-5.68</v>
       </c>
       <c r="L40" t="n">
-        <v>4.78</v>
+        <v>6.17</v>
       </c>
       <c r="M40" t="n">
         <v>0.39</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.18</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H41" t="n">
-        <v>548.2</v>
+        <v>559.85</v>
       </c>
       <c r="I41" t="n">
         <v>551.0025136879284</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.95</v>
       </c>
       <c r="L41" t="n">
-        <v>3.11</v>
+        <v>5.28</v>
       </c>
       <c r="M41" t="n">
         <v>1.81</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.95</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45274</v>
+        <v>45275</v>
       </c>
       <c r="H42" t="n">
-        <v>532.35</v>
+        <v>519.2</v>
       </c>
       <c r="I42" t="n">
         <v>523.0694071085591</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.91</v>
+        <v>-7.26</v>
       </c>
       <c r="L42" t="n">
-        <v>5.22</v>
+        <v>7.78</v>
       </c>
       <c r="M42" t="n">
         <v>0.15</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.5</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45327</v>
+        <v>45328</v>
       </c>
       <c r="H43" t="n">
-        <v>504.8</v>
+        <v>526</v>
       </c>
       <c r="I43" t="n">
         <v>519.2654391550037</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K43" t="n">
-        <v>2.77</v>
+        <v>-1.31</v>
       </c>
       <c r="L43" t="n">
         <v>6.05</v>
@@ -2892,7 +3407,7 @@
         <v>1.19</v>
       </c>
       <c r="N43" t="n">
-        <v>2.51</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>-2.47</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.22</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="H44" t="n">
-        <v>588.15</v>
+        <v>580.3</v>
       </c>
       <c r="I44" t="n">
         <v>581.7545798081203</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K44" t="n">
-        <v>11.82</v>
+        <v>10.32</v>
       </c>
       <c r="L44" t="n">
         <v>5.46</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.82</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H45" t="n">
-        <v>579.75</v>
+        <v>596.15</v>
       </c>
       <c r="I45" t="n">
         <v>590.8932358007763</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>0.09</v>
+        <v>-2.73</v>
       </c>
       <c r="L45" t="n">
         <v>4.2</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.04</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H46" t="n">
-        <v>732.15</v>
+        <v>716.25</v>
       </c>
       <c r="I46" t="n">
         <v>730.6852822889132</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K46" t="n">
-        <v>22.81</v>
+        <v>20.15</v>
       </c>
       <c r="L46" t="n">
         <v>3.75</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H47" t="n">
-        <v>581.4</v>
+        <v>596.85</v>
       </c>
       <c r="I47" t="n">
         <v>582.7086804102421</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K47" t="n">
-        <v>18.83</v>
+        <v>16.67</v>
       </c>
       <c r="L47" t="n">
         <v>2.46</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>8.02</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H48" t="n">
-        <v>556.8</v>
+        <v>536.9</v>
       </c>
       <c r="I48" t="n">
         <v>553.6447019257714</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.71</v>
+        <v>-10.04</v>
       </c>
       <c r="L48" t="n">
-        <v>7.35</v>
+        <v>11.9</v>
       </c>
       <c r="M48" t="n">
-        <v>0.64</v>
+        <v>4.38</v>
       </c>
       <c r="N48" t="n">
         <v>4.57</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>9.08</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="H49" t="n">
-        <v>567.15</v>
+        <v>586.3</v>
       </c>
       <c r="I49" t="n">
         <v>585.6616379659815</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.63</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>7.29</v>
+        <v>12.17</v>
       </c>
       <c r="M49" t="n">
-        <v>1.12</v>
+        <v>2.44</v>
       </c>
       <c r="N49" t="n">
         <v>3.74</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.07</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H50" t="n">
-        <v>631.45</v>
+        <v>623.35</v>
       </c>
       <c r="I50" t="n">
         <v>623.8736037266481</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K50" t="n">
-        <v>7.7</v>
+        <v>6.32</v>
       </c>
       <c r="L50" t="n">
         <v>2.62</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.87</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="H51" t="n">
-        <v>664.55</v>
+        <v>680.35</v>
       </c>
       <c r="I51" t="n">
         <v>671.987264938035</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.61</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>7.32</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M51" t="n">
         <v>0.87</v>
       </c>
       <c r="N51" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O51" t="n">
         <v>-1.28</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.71</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H52" t="n">
-        <v>634.9</v>
+        <v>625.1</v>
       </c>
       <c r="I52" t="n">
         <v>627.8613090372046</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.68</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>7.57</v>
+        <v>8.34</v>
       </c>
       <c r="M52" t="n">
         <v>0.6899999999999999</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="H53" t="n">
-        <v>614.8</v>
+        <v>624.7</v>
       </c>
       <c r="I53" t="n">
         <v>620.519297929512</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K53" t="n">
-        <v>1.65</v>
+        <v>0.06</v>
       </c>
       <c r="L53" t="n">
         <v>4.93</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.7</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H54" t="n">
-        <v>660.95</v>
+        <v>651.8</v>
       </c>
       <c r="I54" t="n">
         <v>657.0025453300208</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K54" t="n">
-        <v>5.8</v>
+        <v>4.34</v>
       </c>
       <c r="L54" t="n">
         <v>3.51</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>9.4</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H55" t="n">
-        <v>546.5</v>
+        <v>561.25</v>
       </c>
       <c r="I55" t="n">
         <v>557.7034692906738</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K55" t="n">
-        <v>16.16</v>
+        <v>13.89</v>
       </c>
       <c r="L55" t="n">
         <v>3.95</v>
       </c>
       <c r="M55" t="n">
-        <v>4.71</v>
+        <v>5.76</v>
       </c>
       <c r="N55" t="n">
         <v>4.83</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.16</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="H56" t="n">
-        <v>522.15</v>
+        <v>509.25</v>
       </c>
       <c r="I56" t="n">
         <v>515.0251433975504</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.97</v>
+        <v>-9.27</v>
       </c>
       <c r="L56" t="n">
         <v>12.94</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>11.25</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H57" t="n">
-        <v>490.35</v>
+        <v>503.65</v>
       </c>
       <c r="I57" t="n">
         <v>502.3571028430522</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K57" t="n">
-        <v>3.71</v>
+        <v>1.1</v>
       </c>
       <c r="L57" t="n">
         <v>3.94</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>9.19</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H58" t="n">
-        <v>494.55</v>
+        <v>470.65</v>
       </c>
       <c r="I58" t="n">
         <v>485.4313755486305</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.81</v>
+        <v>-6.55</v>
       </c>
       <c r="L58" t="n">
-        <v>4.92</v>
+        <v>6.55</v>
       </c>
       <c r="M58" t="n">
         <v>1.94</v>
       </c>
       <c r="N58" t="n">
-        <v>4.18</v>
+        <v>4.83</v>
       </c>
       <c r="O58" t="n">
         <v>2.71</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>35</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8085,7 +8800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.7</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="6">
@@ -8095,7 +8810,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -8105,7 +8820,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
@@ -8115,7 +8830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -8125,7 +8840,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -8135,7 +8850,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138.2</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="11">
@@ -8145,7 +8860,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -8155,7 +8870,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -8165,7 +8880,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.3</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="14">
@@ -8175,7 +8890,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.21</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="15">
@@ -8185,7 +8900,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.55</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="16">
@@ -8195,7 +8910,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.82</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="17">
@@ -8205,7 +8920,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48.37</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="18">
@@ -8215,7 +8930,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.1</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="19">
@@ -8225,7 +8940,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.71</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="20">
@@ -8235,7 +8950,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.97</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="21">
@@ -8255,7 +8970,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -8265,7 +8980,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -8275,7 +8990,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="25">
@@ -8295,7 +9010,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.26</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="27">
@@ -8315,7 +9030,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
